--- a/data/daily/2026-10/2026-10-24.xlsx
+++ b/data/daily/2026-10/2026-10-24.xlsx
@@ -11,7 +11,9 @@
     <sheet name="카카오선물하기_카드형" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="다이소몰" sheetId="3" state="hidden" r:id="rId3"/>
     <sheet name="다이소몰_카드형" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="카테고리통계" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="올리브영" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet name="올리브영_카드형" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="카테고리통계" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1168,7 +1170,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="361950" cy="457200"/>
+    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -1193,14 +1195,39 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1215,17 +1242,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1240,17 +1267,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1265,17 +1292,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1290,17 +1317,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1315,35 +1342,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -1423,7 +1425,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="990600" cy="1238250"/>
+    <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -1448,9 +1450,264 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
@@ -1468,12 +1725,267 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
       <col>4</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -1498,7 +2010,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -1523,7 +2035,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -1548,7 +2060,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -1573,7 +2085,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -1598,7 +2110,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -1623,7 +2135,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -1648,7 +2160,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -2084,22 +2596,26 @@
         <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>16339</v>
+        <v>16340</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>선물용으로 높은 만족도 — 생일이나 기념일 선물로 받아 감동적이고 만족도가 높음</t>
+          <t>높은 선물용 만족도 — 생일이나 건강 챙김용 선물로 주고받기 좋으며 받는 사람의 만족도가 높음</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>피로 및 건강 회복 효과 — 감기 회복 및 입술 터짐 개선 등 건강 관리와 회복에 도움을 줌</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>피로 회복 및 컨디션 개선 — 감기 회복이나 입술 터짐 등 피로 증상 개선에 도움을 줌</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>높은 브랜드 인지도 — 평소에도 자주 먹는 유명한 제품이라 반갑고 신뢰도가 높음</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>부담스러운 제품 가격 — 평소 직접 구매하기에는 가격이 다소 비싼 편임</t>
+          <t>높은 가격대 부담 — 평소 직접 구매해서 먹기에는 가격대가 비싼 편임</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
@@ -2143,21 +2659,21 @@
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>15675</v>
+        <v>15680</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>빠른 배송과 깔끔한 포장 — 배송이 빠르고 포장이 깔끔하여 선물용으로 전달하기 좋음</t>
+          <t>체감되는 피로 회복 효과 — 야근이나 피로 시 섭취하면 활력이 생기고 피로회복 효과가 뛰어남</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>간편한 섭취와 휴대성 — 개별 포장으로 휴대하기 쉽고 섭취 방법이 간편함</t>
+          <t>신속한 배송과 섭취 편의 — 배송이 빠르고 안전하며 간편하게 섭취하기 좋음</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>피로 회복 및 기력 보충 — 섭취 후 피로 회복 및 기력 충전에 도움을 느낌</t>
+          <t>지인 선물용 적합성 — 가족이나 지인에게 마음을 전하는 선물용으로 간편하게 구매하기 좋음</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -2206,17 +2722,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>고급 선물 및 알찬 구성 — 고급스럽고 넉넉한 30개입 구성으로 선물 및 일상 섭취에 실용적임</t>
+          <t>진한 농도와 뛰어난 활력 증진 — 액상 농도가 진하며 체력이 떨어질 때 섭취 시 확실하게 힘이 남</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>진한 농도와 피로 개선 — 액상 농도가 진하며 지칠 때 체력 보충과 피로 회복에 효과적임</t>
+          <t>넉넉한 수량과 휴대 편의성 — 30개입 구성으로 용량이 넉넉하고 하나씩 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>간편한 개별 포장 섭취 — 하나씩 챙겨 먹기 편리하여 일상에서 건강을 관리하기 좋음</t>
+          <t>고급스러운 선물 가치 — 선물 받았을 때 기분이 좋고 고급스러워 선물용으로 매우 유용함</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -2265,23 +2781,23 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>맛있는 젤리 제형 — 과일맛의 쫄깃한 젤리 형태로 물 없이 간식처럼 맛있게 섭취 가능함</t>
+          <t>젤리 형태의 높은 복용 편의성 — 물 없이 간식처럼 씹어 먹을 수 있어 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>바쁜 일상 속 간편 섭취 — 물 없이 씹어서 먹을 수 있어 바쁜 아침에 영양제를 챙기기 용이함</t>
+          <t>거부감 없는 맛있는 맛 — 과일맛의 새콤달콤하고 적당히 말랑한 식감으로 남녀노소 맛있게 먹음</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>포장 개봉의 불편함 — 비닐이나 포장이 잘 뜯어지지 않아 개봉할 때 불편함</t>
+          <t>용기 포장 개봉의 어려움 — 밀봉 포장이 잘 뜯어지지 않아 개봉할 때 인내심이 필요함</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>비타민 같지 않은 제형 — 일반 젤리 과자 같거나 어린이 영양제처럼 느껴질 수 있음</t>
+          <t>어린이 비타민 같은 느낌 — 일반 영양제보다 아동용 젤리 간식처럼 느껴질 수 있음</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -2324,21 +2840,21 @@
         <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>센스 있는 선물 아이템 — 구성이 좋아 선물용으로 주는 사람과 받는 사람 모두 만족함</t>
+          <t>일상 피로 회복 도움 — 피곤할 때 먹으면 기운이 나고 몸과 마음이 상쾌해짐</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>휴대 및 섭취 편의성 — 먹기 편하고 휴대성이 뛰어난 개별 포장 및 액상 형태임</t>
+          <t>휴대 및 복용 간편성 — 휴대하기 편하고 먹기 쉬운 형태로 구성되어 일상에서 잘 챙겨 먹음</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>상쾌한 피로 회복 효과 — 환절기 건강 관리와 피로 회복에 뛰어난 효과를 보임</t>
+          <t>센스 있는 선물용 구성 — 환절기나 생일에 선물용으로 주고받기에 만족도가 큼</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -2387,22 +2903,22 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>섞어 먹는 재미와 달콤함 — 버튼을 눌러 분말과 액상을 섞는 방식이 재미있고 신맛이 적으며 달콤함</t>
+          <t>즉각적인 활력 충전 — 달콤새콤한 맛으로 마신 후 힘이 나고 컨디션이 좋아지는 느낌을 받음</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>고급 포장과 빠른 배송 — 쇼핑백을 챙겨주어 포장이 고급스럽고 배송이 빨라 선물용으로 적합함</t>
+          <t>재미있는 분말 혼합 방식 — 버튼을 눌러 분말과 액상을 직접 섞어 마시는 방식이 흥미로움</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>빠른 컨디션 회복 체감 — 섭취 후 활력이 생기고 컨디션 개선 효과를 체감함</t>
+          <t>고급스러운 포장과 쇼핑백 — 선물용 쇼핑백이 포함되며 포장이 고급스러움</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>버튼 및 비닐 개봉 불편 — 버튼이 뻑뻑하고 비닐 포장을 벗기기 어려워 개봉 시 불편함</t>
+          <t>버튼 및 비닐 개봉의 불편함 — 버튼이 뻑뻑하고 비닐을 벗기기 어려워 어르신들이 섭취하기엔 다소 불편함</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
@@ -2450,17 +2966,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>신속한 배송 서비스 — 배송이 매우 빠르고 안전하게 도착함</t>
+          <t>간편한 액상 제형 — 마시는 액상 타입이라 언제 어디서나 섭취하기 간편함</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>간편한 마시는 액상 타입 — 마시는 액상 형태라 물 없이 편리하게 섭취 가능함</t>
+          <t>피로 해소 및 기운 증진 — 아침이나 피곤할 때 먹으면 기운이 나고 체력이 충전됨</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>활력 증진 및 피로 해소 — 아침이나 피곤할 때 섭취하면 기운이 나고 피로 회복에 도움을 줌</t>
+          <t>빠르고 안전한 배송 — 주문 후 배송이 빠르고 꼼꼼하게 전달됨</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -2470,7 +2986,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -2478,49 +2994,49 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>고함량 비타민C 고려은단 메가도스C 3000 100포 / 분말비타민C</t>
+          <t>'1입 증정' 오쏘몰 바이탈 m/f 남성/여성 선택가능 14+1입 - 시그니처 기프트 에디션 (공식수입)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>고려은단</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>24,900원</t>
+          <t>59,800원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/3252731</t>
+          <t>https://gift.kakao.com/product/8167919</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260909091732_b68718856ae342d0b37c3e36916af86b.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261008180237_441cb42108de40bb9ca4f55e8f361c4c.jpg</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>985</v>
+        <v>788</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>뛰어난 피로 회복 효과 — 고함량 비타민C로 섭취 시 정신이 번쩍 들며 피로 회복에 효과적임</t>
+          <t>확실한 피로 회복 및 활력 증진 — 지치고 바쁠 때 복용 시 활력이 돋고 피로 해소 효과가 뛰어남</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>휴대 및 복용 용이성 — 분말 스틱 포장 형태로 가방에 들고 다니며 챙겨 먹기 편리함</t>
+          <t>복용 및 휴대 편의성 — 배송 상태가 양호하며 한 번에 간편하게 먹기 편함</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>강한 신맛과 물 필수 복용 — 맛이 매우 셔서 단독 복용이 어렵고 물과 함께 마셔야 함</t>
+          <t>호불호 갈리는 약 맛 — 오렌지 맛 감기약 같은 맛이 나서 맛에 호불호가 갈릴 수 있음</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -2529,7 +3045,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -2537,49 +3053,49 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>'1입 증정' 오쏘몰 바이탈 m/f 남성/여성 선택가능 14+1입 - 시그니처 기프트 에디션 (공식수입)</t>
+          <t>고함량 비타민C 고려은단 메가도스C 3000 100포 / 분말비타민C</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>59,800원</t>
+          <t>24,900원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/8167919</t>
+          <t>https://gift.kakao.com/product/3252731</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261008180237_441cb42108de40bb9ca4f55e8f361c4c.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260909091732_b68718856ae342d0b37c3e36916af86b.jpg</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>788</v>
+        <v>987</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>확실한 활력 증진 효과 — 바쁜 직장인의 피로 개선과 활력 증진에 확실한 효과를 줌</t>
+          <t>고함량 비타민C의 피로 회복 — 3000mg 고함량으로 섭취 시 정신이 번쩍 들 만큼 피로 회복에 효과적임</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>편리한 섭취와 빠른 배송 — 배송 상태가 양호하며 먹기 편한 구성으로 만족스러움</t>
+          <t>개별 포장의 우수한 휴대성 — 스틱 개별 포장이라 가방에 넣고 다니며 챙겨 먹기 든든함</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>호불호 갈리는 약 맛 — 오렌지 맛 감기약 느낌이 나 맛에 대한 호불호가 갈림</t>
+          <t>매우 강한 신맛과 물 필수 복용 — 신맛이 매우 강해서 물 없이 먹기 힘들고 반드시 물과 함께 먹어야 함</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -2596,62 +3112,58 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 30+1입 (소비기한 2027년 4월 30일~)</t>
+          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>85,000원</t>
+          <t>52,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/11691875</t>
+          <t>https://gift.kakao.com/product/10903147</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261013084013_bcc76e1c941c4974956d6ed2bdcce13d.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261006173014_9a46de80b829480796c23d0cd4a75de9.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>131</v>
+        <v>847</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>혓바늘 및 피로 개선 — 섭취 후 피로 및 혓바늘 완화에 빠르고 확실한 효과를 보임</t>
+          <t>뛰어난 피로 해소 효과 — 아침에 하나씩 복용하면 커피 없이도 피로가 가시고 상쾌함</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>신속 배송과 할인 혜택 — 배송이 빠르며 할인 행사 시 가성비 높게 구매 가능함</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>짧은 유통기한의 아쉬움 — 수령한 제품의 유통기한이 기대보다 다소 짧음</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>부담스러운 정가 가격 — 이벤트 미적용 시 가격 부담이 다소 존재하는 편임</t>
-        </is>
-      </c>
+          <t>간편한 휴대 및 섭취 — 한 병씩 개별 포장되어 있어 가지고 다니며 간단하게 마시기 편리함</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>빠른 배송과 꼼꼼한 포장 — 포장이 철저하고 배송이 신속하게 완료됨</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
     <row r="12" ht="38" customHeight="1">
       <c r="B12" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -2659,48 +3171,48 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>부족함 없이 인기상품만 넣은 [한끼통살]닭가슴살 Non-stop 올인원패키지 36팩+ [증정]현미크리스피 닭가슴살 오리지널 1개</t>
+          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) +파로저당견과류바 증정</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>57,900원</t>
+          <t>22,900원</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12201735</t>
+          <t>https://gift.kakao.com/product/13180362</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261022235449_5267b277d2d34792874c370e57c948d8.png</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261021101500_a33c07ee9dfe4879b427c57a18d9ce91.jpg</t>
         </is>
       </c>
       <c r="I12" t="n">
         <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>31</v>
+        <v>951</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>다양한 맛과 부드러운 살 — 36가지의 다양한 맛 구성으로 질리지 않으며 고기가 부드러움</t>
+          <t>가성비 뛰어난 할인가 구매 — 할인 및 톡딜 행사로 합리적인 가격에 저렴하게 구매 가능함</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>간편한 전자레인지 조리 — 전자레인지에 간단히 데워 한 끼 식단으로 먹기 편리함</t>
+          <t>달콤하고 편안한 맛 — 맛이 달콤하여 부담 없이 꾸준히 먹기 편함</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>빠른 누락 대처 서비스 — 누락 건 발생 시 빠르게 문의에 대처하여 신속히 재발송해 줌</t>
+          <t>푸짐한 구성 및 증정품 — 저당견과류바와 단백칩 등 기대 이상의 사은품이 넉넉하게 제공됨</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2710,7 +3222,7 @@
     <row r="13" ht="38" customHeight="1">
       <c r="B13" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2718,48 +3230,48 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) +파로저당견과류바 증정</t>
+          <t>부족함 없이 인기상품만 넣은 [한끼통살]닭가슴살 Non-stop 올인원패키지 36팩+ [증정]현미크리스피 닭가슴살 오리지널 1개</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>22,900원</t>
+          <t>57,900원</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13180362</t>
+          <t>https://gift.kakao.com/product/12201735</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261021101500_a33c07ee9dfe4879b427c57a18d9ce91.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261022235449_5267b277d2d34792874c370e57c948d8.png</t>
         </is>
       </c>
       <c r="I13" t="n">
         <v>4</v>
       </c>
       <c r="J13" t="n">
-        <v>951</v>
+        <v>31</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>저렴한 할인 구매 기회 — 톡딜 등 할인 행사 시 저렴하게 구매할 수 있어 만족스러움</t>
+          <t>다양한 맛과 부드러운 식감 — 36가지 다양한 종류로 식단이 질리지 않으며 고깃살이 부드러움</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>달콤하고 편안한 맛 — 맛이 달콤하여 매일 부담 없이 편하게 먹을 수 있음</t>
+          <t>간편한 전자레인지 조리 — 전자레인지로 간단히 데워 먹을 수 있어 식사 준비가 간편함</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>푸짐한 사은품 증정 — 저당 견과류바와 단백칩 등 푸짐한 사은품이 동봉되어 도착함</t>
+          <t>신속한 누락 대처 — 수량 누락 문의 시 즉각적으로 다시 보내주는 신속한 고객 대응을 보임</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2808,17 +3320,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>확실한 숙취 해소 효과 — 음주 전후 섭취 시 다음 날 머리가 덜 아프고 숙취가 완화됨</t>
+          <t>확실한 숙취 해소 도움 — 음주 전후 섭취 시 다음 날 숙취가 적고 머리 아픔이 덜함</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>개별 스틱 포장의 휴대성 — 한 포씩 개별 포장된 스틱 형태로 들고 다니기 편리함</t>
+          <t>거부감 없는 달콤한 맛 — 텁텁하지 않고 달콤한 액상이라 거부감 없이 쉽게 넘어감</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>물 없이 먹는 달콤한 맛 — 액상 타입이라 물 없이 섭취할 수 있고 달콤하여 거부감이 없음</t>
+          <t>스틱 형태의 휴대 및 복용 편의 — 물 없이 바로 먹는 스틱 형태라 술자리 전후 휴대하며 챙기기 용이함</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2867,17 +3379,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>속 편한 소화 개선 효과 — 식후 섭취 시 더부룩한 속이 편안해지도록 도와줌</t>
+          <t>더부룩한 속을 가라앉히는 소화 개선 — 식후 속 더부룩함이 줄어들고 속이 편안해짐</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>고소하고 맛있는 풍미 — 미숫가루처럼 꼬수운 맛으로 부담 없이 맛있게 먹을 수 있음</t>
+          <t>고소한 미숫가루 맛 — 미숫가루처럼 꼬수운 맛으로 부담 없이 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>고급 포장과 알찬 사은품 — 선물용 패키지가 고급스럽고 푸짐한 사은품을 함께 제공함</t>
+          <t>고급스러운 포장과 알찬 증정품 — 선물용 패키지가 고급스럽고 견과류바 등 사은품 구성이 푸짐함</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2926,26 +3438,30 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>질리지 않는 다양한 구성 — 떡볶이맛 등 다양하게 구성되어 맛있게 먹을 수 있음</t>
+          <t>맛있는 맛과 다채로운 구성 — 떡볶이맛 등 구성이 다채롭고 맛있게 식단을 관리할 수 있음</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>합리적인 할인 가격 — 할인가로 구매 시 가성비가 훌륭하여 만족스러움</t>
+          <t>이벤트 할인가의 가성비 — 할인 행사 구매 시 가성비가 매우 뛰어남</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>수량 누락 및 임의 대체 — 제품 수량이 부족하거나 사전 안내 없이 다른 맛으로 대체됨</t>
+          <t>수량 누락 및 임의 구성 변경 — 상품 수량이 안 맞거나 원치 않는 맛으로 대체 배송되는 문제가 있음</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>제품 해동 및 강한 간 — 배송 시 약간 녹아 오거나 일부 제품의 간이 다소 세게 느껴짐</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr"/>
+          <t>느리고 답답한 고객 대응 — 누락 및 문제 발생 시 CS 응대 처리가 더딤</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>다소 강한 간과 포장 녹음 — 생각보다 간이 세게 느껴질 수 있으며 배송 시 약간 녹아 도착함</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="38" customHeight="1">
       <c r="B17" t="inlineStr">
@@ -2985,26 +3501,26 @@
         <v>4</v>
       </c>
       <c r="J17" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>담백한 계란 흰자 구성 — 노른자 없이 흰자만으로 구성되어 칼로리 부담이 적고 퍽퍽하지 않음</t>
+          <t>계란 흰자 중심의 깔끔한 구성 — 노른자가 없어 퍽퍽하지 않고 삶은 계란 흰자 본연의 촉촉한 맛임</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>비린내 없는 다양한 맛 — 비린 맛이 없고 구운 맛 등 다양하여 질리지 않음</t>
+          <t>조리와 껍질 처리가 불필요한 간편함 — 계란을 삶거나 껍질을 끌 필요가 없어 어디서나 간식으로 바로 먹기 편함</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>간편한 섭취와 긴 포만감 — 껍질을 끌 필요 없어 간편하며 먹은 후 포만감이 오래 지속됨</t>
+          <t>비린내 없는 낮은 칼로리 — 계란 특유의 비린내가 없으며 칼로리 부담 없이 단백질 채우기에 적합함</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>깨끗하지 않은 외관 박스 — 배송 시 제품 외관 박스가 재활용한 것처럼 다소 깨끗하지 않음</t>
+          <t>외관 택배 박스 위생 불만 — 제품 상자는 양호하나 외관 포장 박스가 재활용된 듯 깨끗하지 않음</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
@@ -3052,17 +3568,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>아티스트 포카 증정 — 좋아하는 아티스트의 포토카드와 엽서가 포함되어 만족스러움</t>
+          <t>기대 이상의 맛있는 맛 — 쿠키앤크림, 소다아이스크림 등 기존 효소와 달리 맛있게 섭취 가능함</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>맛있는 디저트 풍미 — 쿠키앤크림, 소다아이스크림 맛 등 맛이 뛰어남</t>
+          <t>풍성한 증정품과 굿즈 구성 — 포토카드, 엽서 및 단백질바 등 푸짐하고 매력적인 구성품을 제공함</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>알찬 단백질바 구성 — 추가 증정된 단백질바도 맛이 좋아 출출할 때 간식으로 좋음</t>
+          <t>과식 후 속 편한 소화 효과 — 과식 후 섭취 시 소화에 도움이 되고 속이 편안해짐</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -3111,17 +3627,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>촉촉하고 맛있는 식감 — 닭가슴살이 퍽퍽하지 않고 촉촉하며 떡볶이맛 등이 맛있음</t>
+          <t>촉촉하고 맛있는 닭가슴살 — 퍽퍽하지 않고 촉촉하며 맛이 다양하여 질리지 않음</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>간단한 전자레인지 조리 — 전자레인지에 데우기만 하면 되어 간편함</t>
+          <t>전자레인지 조리의 간편함 — 전자레인지에 간단히 데워 먹을 수 있어 식사 대용으로 편함</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>가성비 높은 식단 관리 — 구성이 알차고 가격이 저렴하여 식단 관리에 적합함</t>
+          <t>식단 관리에 용이한 낮은 칼로리 — 칼로리가 낮아 다이어트 및 건강 관리 식단으로 이용하기 좋음</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -3131,7 +3647,7 @@
     <row r="20" ht="38" customHeight="1">
       <c r="B20" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -3139,48 +3655,48 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 파로효소 캡슐레이션 3개월(+선물포장)+쇼핑백+그린캡슐레이션효소 증정</t>
+          <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분+앰플 2입 추가 증정</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>아일로</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>64,900원</t>
+          <t>65,900원</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13255641</t>
+          <t>https://gift.kakao.com/product/4965835</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261022082137_8413f613a8ac4edb9b69847f419517ca.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261021173253_c716df66353b42e9b0e73e5db0962008.jpg</t>
         </is>
       </c>
       <c r="I20" t="n">
         <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>33</v>
+        <v>760</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>신속한 소화와 편안한 속 — 식후 섭취 시 빠르게 소화되어 속 더부룩함이 개선됨</t>
+          <t>고급스러운 포장과 플리츠백 증정 — 포장이 매우 고급스럽고 예쁘며 플리츠백 구성으로 선물용에 최적임</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>부드러운 분말과 고구마 맛 — 분말이 고와 목에 걸리지 않으며 달콤한 고구마 맛으로 맛있음</t>
+          <t>맛있는 앰플 제형의 편의성 — 맛이 상큼하고 좋으며 앰플 형태라 마시기 편리함</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>빠른 배송과 쇼핑백 증정 — 배송이 빠르고 선물용 쇼핑백이 함께 동봉됨</t>
+          <t>피부 탄력 및 피로 개선 기대 — 섭취 후 피로감이 덜하고 피부 촉촉함과 탄력 케어에 도움을 줌</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3190,7 +3706,7 @@
     <row r="21" ht="38" customHeight="1">
       <c r="B21" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -3198,48 +3714,48 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분+앰플 2입 추가 증정</t>
+          <t>[그레인온] 골드 파로효소 캡슐레이션 3개월(+선물포장)+쇼핑백+그린캡슐레이션효소 증정</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>아일로</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>65,900원</t>
+          <t>64,900원</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/4965835</t>
+          <t>https://gift.kakao.com/product/13255641</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261021173253_c716df66353b42e9b0e73e5db0962008.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261022082137_8413f613a8ac4edb9b69847f419517ca.jpg</t>
         </is>
       </c>
       <c r="I21" t="n">
         <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>760</v>
+        <v>33</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>고급스럽고 예쁜 패키지 — 선물포장과 플리츠백 구성이 고급스럽고 예쁨</t>
+          <t>달콤한 고구마맛과 부드러운 목넘김 — 달달한 고구마맛으로 맛있으며 입자가 고와 목에 걸리지 않음</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>맛있는 액상 섭취 — 비린 맛 없이 맛이 좋아 하루 한 병씩 챙겨 먹기 편함</t>
+          <t>더부룩함 없는 빠른 소화 — 식후 섭취 시 답답하고 더부룩한 속이 금방 편안해짐</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>피부 촉촉함 체감 — 섭취 시 피부에 탄력과 촉촉함이 생기는 느낌을 받음</t>
+          <t>빠른 배송과 선물용 패키지 — 배송이 빠르고 쇼핑백 및 포장 구성이 고급스러워 선물하기 적합함</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3392,12 +3908,12 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
           <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -3449,17 +3965,17 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>오쏘몰</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
           <t>고려은단</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>오쏘몰</t>
-        </is>
-      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>닥터블릿</t>
         </is>
       </c>
     </row>
@@ -3506,17 +4022,17 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>'1입 증정' 오쏘몰 바이탈 m/f 남성/여성 선택가능 14+1입 - 시그니처 기프트 에디션 (공식수입)</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
           <t>고함량 비타민C 고려은단 메가도스C 3000 100포 / 분말비타민C</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>'1입 증정' 오쏘몰 바이탈 m/f 남성/여성 선택가능 14+1입 - 시그니처 기프트 에디션 (공식수입)</t>
-        </is>
-      </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 30+1입 (소비기한 2027년 4월 30일~)</t>
+          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병</t>
         </is>
       </c>
     </row>
@@ -3564,10 +4080,10 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>16339</v>
+        <v>16340</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>15675</v>
+        <v>15680</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>3423</v>
@@ -3576,7 +4092,7 @@
         <v>6534</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>1803</v>
@@ -3585,13 +4101,13 @@
         <v>8765</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>985</v>
+        <v>788</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>788</v>
+        <v>987</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>131</v>
+        <v>847</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1">
@@ -3602,67 +4118,69 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>선물용으로 높은 만족도 — 생일이나 기념일 선물로 받아 감동적이고 만족도가 높음
-피로 및 건강 회복 효과 — 감기 회복 및 입술 터짐 개선 등 건강 관리와 회복에 도움을 줌</t>
+          <t>높은 선물용 만족도 — 생일이나 건강 챙김용 선물로 주고받기 좋으며 받는 사람의 만족도가 높음
+피로 회복 및 컨디션 개선 — 감기 회복이나 입술 터짐 등 피로 증상 개선에 도움을 줌
+높은 브랜드 인지도 — 평소에도 자주 먹는 유명한 제품이라 반갑고 신뢰도가 높음</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>빠른 배송과 깔끔한 포장 — 배송이 빠르고 포장이 깔끔하여 선물용으로 전달하기 좋음
-간편한 섭취와 휴대성 — 개별 포장으로 휴대하기 쉽고 섭취 방법이 간편함
-피로 회복 및 기력 보충 — 섭취 후 피로 회복 및 기력 충전에 도움을 느낌</t>
+          <t>체감되는 피로 회복 효과 — 야근이나 피로 시 섭취하면 활력이 생기고 피로회복 효과가 뛰어남
+신속한 배송과 섭취 편의 — 배송이 빠르고 안전하며 간편하게 섭취하기 좋음
+지인 선물용 적합성 — 가족이나 지인에게 마음을 전하는 선물용으로 간편하게 구매하기 좋음</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>고급 선물 및 알찬 구성 — 고급스럽고 넉넉한 30개입 구성으로 선물 및 일상 섭취에 실용적임
-진한 농도와 피로 개선 — 액상 농도가 진하며 지칠 때 체력 보충과 피로 회복에 효과적임
-간편한 개별 포장 섭취 — 하나씩 챙겨 먹기 편리하여 일상에서 건강을 관리하기 좋음</t>
+          <t>진한 농도와 뛰어난 활력 증진 — 액상 농도가 진하며 체력이 떨어질 때 섭취 시 확실하게 힘이 남
+넉넉한 수량과 휴대 편의성 — 30개입 구성으로 용량이 넉넉하고 하나씩 챙겨 먹기 편함
+고급스러운 선물 가치 — 선물 받았을 때 기분이 좋고 고급스러워 선물용으로 매우 유용함</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 젤리 제형 — 과일맛의 쫄깃한 젤리 형태로 물 없이 간식처럼 맛있게 섭취 가능함
-바쁜 일상 속 간편 섭취 — 물 없이 씹어서 먹을 수 있어 바쁜 아침에 영양제를 챙기기 용이함</t>
+          <t>젤리 형태의 높은 복용 편의성 — 물 없이 간식처럼 씹어 먹을 수 있어 챙겨 먹기 편함
+거부감 없는 맛있는 맛 — 과일맛의 새콤달콤하고 적당히 말랑한 식감으로 남녀노소 맛있게 먹음</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>센스 있는 선물 아이템 — 구성이 좋아 선물용으로 주는 사람과 받는 사람 모두 만족함
-휴대 및 섭취 편의성 — 먹기 편하고 휴대성이 뛰어난 개별 포장 및 액상 형태임
-상쾌한 피로 회복 효과 — 환절기 건강 관리와 피로 회복에 뛰어난 효과를 보임</t>
+          <t>일상 피로 회복 도움 — 피곤할 때 먹으면 기운이 나고 몸과 마음이 상쾌해짐
+휴대 및 복용 간편성 — 휴대하기 편하고 먹기 쉬운 형태로 구성되어 일상에서 잘 챙겨 먹음
+센스 있는 선물용 구성 — 환절기나 생일에 선물용으로 주고받기에 만족도가 큼</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>섞어 먹는 재미와 달콤함 — 버튼을 눌러 분말과 액상을 섞는 방식이 재미있고 신맛이 적으며 달콤함
-고급 포장과 빠른 배송 — 쇼핑백을 챙겨주어 포장이 고급스럽고 배송이 빨라 선물용으로 적합함
-빠른 컨디션 회복 체감 — 섭취 후 활력이 생기고 컨디션 개선 효과를 체감함</t>
+          <t>즉각적인 활력 충전 — 달콤새콤한 맛으로 마신 후 힘이 나고 컨디션이 좋아지는 느낌을 받음
+재미있는 분말 혼합 방식 — 버튼을 눌러 분말과 액상을 직접 섞어 마시는 방식이 흥미로움
+고급스러운 포장과 쇼핑백 — 선물용 쇼핑백이 포함되며 포장이 고급스러움</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>신속한 배송 서비스 — 배송이 매우 빠르고 안전하게 도착함
-간편한 마시는 액상 타입 — 마시는 액상 형태라 물 없이 편리하게 섭취 가능함
-활력 증진 및 피로 해소 — 아침이나 피곤할 때 섭취하면 기운이 나고 피로 회복에 도움을 줌</t>
+          <t>간편한 액상 제형 — 마시는 액상 타입이라 언제 어디서나 섭취하기 간편함
+피로 해소 및 기운 증진 — 아침이나 피곤할 때 먹으면 기운이 나고 체력이 충전됨
+빠르고 안전한 배송 — 주문 후 배송이 빠르고 꼼꼼하게 전달됨</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 피로 회복 효과 — 고함량 비타민C로 섭취 시 정신이 번쩍 들며 피로 회복에 효과적임
-휴대 및 복용 용이성 — 분말 스틱 포장 형태로 가방에 들고 다니며 챙겨 먹기 편리함</t>
+          <t>확실한 피로 회복 및 활력 증진 — 지치고 바쁠 때 복용 시 활력이 돋고 피로 해소 효과가 뛰어남
+복용 및 휴대 편의성 — 배송 상태가 양호하며 한 번에 간편하게 먹기 편함</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>확실한 활력 증진 효과 — 바쁜 직장인의 피로 개선과 활력 증진에 확실한 효과를 줌
-편리한 섭취와 빠른 배송 — 배송 상태가 양호하며 먹기 편한 구성으로 만족스러움</t>
+          <t>고함량 비타민C의 피로 회복 — 3000mg 고함량으로 섭취 시 정신이 번쩍 들 만큼 피로 회복에 효과적임
+개별 포장의 우수한 휴대성 — 스틱 개별 포장이라 가방에 넣고 다니며 챙겨 먹기 든든함</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>혓바늘 및 피로 개선 — 섭취 후 피로 및 혓바늘 완화에 빠르고 확실한 효과를 보임
-신속 배송과 할인 혜택 — 배송이 빠르며 할인 행사 시 가성비 높게 구매 가능함</t>
+          <t>뛰어난 피로 해소 효과 — 아침에 하나씩 복용하면 커피 없이도 피로가 가시고 상쾌함
+간편한 휴대 및 섭취 — 한 병씩 개별 포장되어 있어 가지고 다니며 간단하게 마시기 편리함
+빠른 배송과 꼼꼼한 포장 — 포장이 철저하고 배송이 신속하게 완료됨</t>
         </is>
       </c>
     </row>
@@ -3674,40 +4192,35 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>부담스러운 제품 가격 — 평소 직접 구매하기에는 가격이 다소 비싼 편임</t>
+          <t>높은 가격대 부담 — 평소 직접 구매해서 먹기에는 가격대가 비싼 편임</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>포장 개봉의 불편함 — 비닐이나 포장이 잘 뜯어지지 않아 개봉할 때 불편함
-비타민 같지 않은 제형 — 일반 젤리 과자 같거나 어린이 영양제처럼 느껴질 수 있음</t>
+          <t>용기 포장 개봉의 어려움 — 밀봉 포장이 잘 뜯어지지 않아 개봉할 때 인내심이 필요함
+어린이 비타민 같은 느낌 — 일반 영양제보다 아동용 젤리 간식처럼 느껴질 수 있음</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>버튼 및 비닐 개봉 불편 — 버튼이 뻑뻑하고 비닐 포장을 벗기기 어려워 개봉 시 불편함</t>
+          <t>버튼 및 비닐 개봉의 불편함 — 버튼이 뻑뻑하고 비닐을 벗기기 어려워 어르신들이 섭취하기엔 다소 불편함</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>강한 신맛과 물 필수 복용 — 맛이 매우 셔서 단독 복용이 어렵고 물과 함께 마셔야 함</t>
+          <t>호불호 갈리는 약 맛 — 오렌지 맛 감기약 같은 맛이 나서 맛에 호불호가 갈릴 수 있음</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>호불호 갈리는 약 맛 — 오렌지 맛 감기약 느낌이 나 맛에 대한 호불호가 갈림</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>짧은 유통기한의 아쉬움 — 수령한 제품의 유통기한이 기대보다 다소 짧음
-부담스러운 정가 가격 — 이벤트 미적용 시 가격 부담이 다소 존재하는 편임</t>
-        </is>
-      </c>
+          <t>매우 강한 신맛과 물 필수 복용 — 신맛이 매우 강해서 물 없이 먹기 힘들고 반드시 물과 함께 먹어야 함</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -3752,17 +4265,17 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>59,800원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
           <t>24,900원</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>59,800원</t>
-        </is>
-      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>85,000원</t>
+          <t>52,900원</t>
         </is>
       </c>
     </row>
@@ -3905,52 +4418,52 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>피부/미용</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
         </is>
       </c>
     </row>
@@ -3962,52 +4475,52 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
+          <t>그레인온</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
           <t>한끼통살</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>알디콤</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>그레인온</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>알디콤</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>한끼통살</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>가농</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>그레인온</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>한끼통살</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>가농</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>아일로</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
         <is>
           <t>그레인온</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>한끼통살</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>그레인온</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>아일로</t>
         </is>
       </c>
     </row>
@@ -4019,14 +4532,14 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
+          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) +파로저당견과류바 증정</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
           <t>부족함 없이 인기상품만 넣은 [한끼통살]닭가슴살 Non-stop 올인원패키지 36팩+ [증정]현미크리스피 닭가슴살 오리지널 1개</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) +파로저당견과류바 증정</t>
-        </is>
-      </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
           <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
@@ -4059,12 +4572,12 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
+          <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분+앰플 2입 추가 증정</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
           <t>[그레인온] 골드 파로효소 캡슐레이션 3개월(+선물포장)+쇼핑백+그린캡슐레이션효소 증정</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분+앰플 2입 추가 증정</t>
         </is>
       </c>
     </row>
@@ -4112,10 +4625,10 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
+        <v>951</v>
+      </c>
+      <c r="D19" s="3" t="n">
         <v>31</v>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>951</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>109</v>
@@ -4127,7 +4640,7 @@
         <v>162</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>278</v>
@@ -4136,10 +4649,10 @@
         <v>70</v>
       </c>
       <c r="K19" s="3" t="n">
+        <v>760</v>
+      </c>
+      <c r="L19" s="3" t="n">
         <v>33</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>760</v>
       </c>
     </row>
     <row r="20" ht="90" customHeight="1">
@@ -4150,75 +4663,75 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>다양한 맛과 부드러운 살 — 36가지의 다양한 맛 구성으로 질리지 않으며 고기가 부드러움
-간편한 전자레인지 조리 — 전자레인지에 간단히 데워 한 끼 식단으로 먹기 편리함
-빠른 누락 대처 서비스 — 누락 건 발생 시 빠르게 문의에 대처하여 신속히 재발송해 줌</t>
+          <t>가성비 뛰어난 할인가 구매 — 할인 및 톡딜 행사로 합리적인 가격에 저렴하게 구매 가능함
+달콤하고 편안한 맛 — 맛이 달콤하여 부담 없이 꾸준히 먹기 편함
+푸짐한 구성 및 증정품 — 저당견과류바와 단백칩 등 기대 이상의 사은품이 넉넉하게 제공됨</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>저렴한 할인 구매 기회 — 톡딜 등 할인 행사 시 저렴하게 구매할 수 있어 만족스러움
-달콤하고 편안한 맛 — 맛이 달콤하여 매일 부담 없이 편하게 먹을 수 있음
-푸짐한 사은품 증정 — 저당 견과류바와 단백칩 등 푸짐한 사은품이 동봉되어 도착함</t>
+          <t>다양한 맛과 부드러운 식감 — 36가지 다양한 종류로 식단이 질리지 않으며 고깃살이 부드러움
+간편한 전자레인지 조리 — 전자레인지로 간단히 데워 먹을 수 있어 식사 준비가 간편함
+신속한 누락 대처 — 수량 누락 문의 시 즉각적으로 다시 보내주는 신속한 고객 대응을 보임</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>확실한 숙취 해소 효과 — 음주 전후 섭취 시 다음 날 머리가 덜 아프고 숙취가 완화됨
-개별 스틱 포장의 휴대성 — 한 포씩 개별 포장된 스틱 형태로 들고 다니기 편리함
-물 없이 먹는 달콤한 맛 — 액상 타입이라 물 없이 섭취할 수 있고 달콤하여 거부감이 없음</t>
+          <t>확실한 숙취 해소 도움 — 음주 전후 섭취 시 다음 날 숙취가 적고 머리 아픔이 덜함
+거부감 없는 달콤한 맛 — 텁텁하지 않고 달콤한 액상이라 거부감 없이 쉽게 넘어감
+스틱 형태의 휴대 및 복용 편의 — 물 없이 바로 먹는 스틱 형태라 술자리 전후 휴대하며 챙기기 용이함</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>속 편한 소화 개선 효과 — 식후 섭취 시 더부룩한 속이 편안해지도록 도와줌
-고소하고 맛있는 풍미 — 미숫가루처럼 꼬수운 맛으로 부담 없이 맛있게 먹을 수 있음
-고급 포장과 알찬 사은품 — 선물용 패키지가 고급스럽고 푸짐한 사은품을 함께 제공함</t>
+          <t>더부룩한 속을 가라앉히는 소화 개선 — 식후 속 더부룩함이 줄어들고 속이 편안해짐
+고소한 미숫가루 맛 — 미숫가루처럼 꼬수운 맛으로 부담 없이 챙겨 먹기 좋음
+고급스러운 포장과 알찬 증정품 — 선물용 패키지가 고급스럽고 견과류바 등 사은품 구성이 푸짐함</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>질리지 않는 다양한 구성 — 떡볶이맛 등 다양하게 구성되어 맛있게 먹을 수 있음
-합리적인 할인 가격 — 할인가로 구매 시 가성비가 훌륭하여 만족스러움</t>
+          <t>맛있는 맛과 다채로운 구성 — 떡볶이맛 등 구성이 다채롭고 맛있게 식단을 관리할 수 있음
+이벤트 할인가의 가성비 — 할인 행사 구매 시 가성비가 매우 뛰어남</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>담백한 계란 흰자 구성 — 노른자 없이 흰자만으로 구성되어 칼로리 부담이 적고 퍽퍽하지 않음
-비린내 없는 다양한 맛 — 비린 맛이 없고 구운 맛 등 다양하여 질리지 않음
-간편한 섭취와 긴 포만감 — 껍질을 끌 필요 없어 간편하며 먹은 후 포만감이 오래 지속됨</t>
+          <t>계란 흰자 중심의 깔끔한 구성 — 노른자가 없어 퍽퍽하지 않고 삶은 계란 흰자 본연의 촉촉한 맛임
+조리와 껍질 처리가 불필요한 간편함 — 계란을 삶거나 껍질을 끌 필요가 없어 어디서나 간식으로 바로 먹기 편함
+비린내 없는 낮은 칼로리 — 계란 특유의 비린내가 없으며 칼로리 부담 없이 단백질 채우기에 적합함</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>아티스트 포카 증정 — 좋아하는 아티스트의 포토카드와 엽서가 포함되어 만족스러움
-맛있는 디저트 풍미 — 쿠키앤크림, 소다아이스크림 맛 등 맛이 뛰어남
-알찬 단백질바 구성 — 추가 증정된 단백질바도 맛이 좋아 출출할 때 간식으로 좋음</t>
+          <t>기대 이상의 맛있는 맛 — 쿠키앤크림, 소다아이스크림 등 기존 효소와 달리 맛있게 섭취 가능함
+풍성한 증정품과 굿즈 구성 — 포토카드, 엽서 및 단백질바 등 푸짐하고 매력적인 구성품을 제공함
+과식 후 속 편한 소화 효과 — 과식 후 섭취 시 소화에 도움이 되고 속이 편안해짐</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>촉촉하고 맛있는 식감 — 닭가슴살이 퍽퍽하지 않고 촉촉하며 떡볶이맛 등이 맛있음
-간단한 전자레인지 조리 — 전자레인지에 데우기만 하면 되어 간편함
-가성비 높은 식단 관리 — 구성이 알차고 가격이 저렴하여 식단 관리에 적합함</t>
+          <t>촉촉하고 맛있는 닭가슴살 — 퍽퍽하지 않고 촉촉하며 맛이 다양하여 질리지 않음
+전자레인지 조리의 간편함 — 전자레인지에 간단히 데워 먹을 수 있어 식사 대용으로 편함
+식단 관리에 용이한 낮은 칼로리 — 칼로리가 낮아 다이어트 및 건강 관리 식단으로 이용하기 좋음</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>신속한 소화와 편안한 속 — 식후 섭취 시 빠르게 소화되어 속 더부룩함이 개선됨
-부드러운 분말과 고구마 맛 — 분말이 고와 목에 걸리지 않으며 달콤한 고구마 맛으로 맛있음
-빠른 배송과 쇼핑백 증정 — 배송이 빠르고 선물용 쇼핑백이 함께 동봉됨</t>
+          <t>고급스러운 포장과 플리츠백 증정 — 포장이 매우 고급스럽고 예쁘며 플리츠백 구성으로 선물용에 최적임
+맛있는 앰플 제형의 편의성 — 맛이 상큼하고 좋으며 앰플 형태라 마시기 편리함
+피부 탄력 및 피로 개선 기대 — 섭취 후 피로감이 덜하고 피부 촉촉함과 탄력 케어에 도움을 줌</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>고급스럽고 예쁜 패키지 — 선물포장과 플리츠백 구성이 고급스럽고 예쁨
-맛있는 액상 섭취 — 비린 맛 없이 맛이 좋아 하루 한 병씩 챙겨 먹기 편함
-피부 촉촉함 체감 — 섭취 시 피부에 탄력과 촉촉함이 생기는 느낌을 받음</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="60" customHeight="1">
+          <t>달콤한 고구마맛과 부드러운 목넘김 — 달달한 고구마맛으로 맛있으며 입자가 고와 목에 걸리지 않음
+더부룩함 없는 빠른 소화 — 식후 섭취 시 답답하고 더부룩한 속이 금방 편안해짐
+빠른 배송과 선물용 패키지 — 배송이 빠르고 쇼핑백 및 포장 구성이 고급스러워 선물하기 적합함</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="90" customHeight="1">
       <c r="B21" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
@@ -4230,13 +4743,14 @@
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>수량 누락 및 임의 대체 — 제품 수량이 부족하거나 사전 안내 없이 다른 맛으로 대체됨
-제품 해동 및 강한 간 — 배송 시 약간 녹아 오거나 일부 제품의 간이 다소 세게 느껴짐</t>
+          <t>수량 누락 및 임의 구성 변경 — 상품 수량이 안 맞거나 원치 않는 맛으로 대체 배송되는 문제가 있음
+느리고 답답한 고객 대응 — 누락 및 문제 발생 시 CS 응대 처리가 더딤
+다소 강한 간과 포장 녹음 — 생각보다 간이 세게 느껴질 수 있으며 배송 시 약간 녹아 도착함</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>깨끗하지 않은 외관 박스 — 배송 시 제품 외관 박스가 재활용한 것처럼 다소 깨끗하지 않음</t>
+          <t>외관 택배 박스 위생 불만 — 제품 상자는 양호하나 외관 포장 박스가 재활용된 듯 깨끗하지 않음</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr"/>
@@ -4252,14 +4766,14 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
+          <t>22,900원</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
           <t>57,900원</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>22,900원</t>
-        </is>
-      </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
           <t>33,200원</t>
@@ -4292,12 +4806,12 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
+          <t>65,900원</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
           <t>64,900원</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>65,900원</t>
         </is>
       </c>
     </row>
@@ -4487,7 +5001,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4495,12 +5009,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>락피도 티니핑 쾌변스틱 12포 12일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>락피도</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -4510,28 +5024,28 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=951817121&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260226/d2rmOd3RsE864TxS1ei6951817121_00_01d2rmOd3RsE864TxS1ei6.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
       <c r="I2" t="n">
         <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>436</v>
+        <v>7586</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>자극 없는 시원한 쾌변 — 배가 아프거나 불편함 없이 자연스러운 쾌변을 도와줌</t>
+          <t>부담 없는 뛰어난 가성비 — 가격대가 매우 저렴하여 부담 없이 꾸준히 복용 가능함</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>맛있는 개별 포장 스틱 — 맛이 좋고 1포씩 개별 포장되어 간편하게 먹을 수 있음</t>
+          <t>하루 한 알의 간편 복용 — 캡슐 크기가 적당하여 하루 한 알씩 식후 챙겨 먹기 편리함</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
@@ -4542,7 +5056,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4550,58 +5064,58 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>대웅제약 맥주효모 비오틴 30정 30일분</t>
+          <t>홀베리 레몬 비타C 500 10개입</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>홀베리</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000140&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=030086178&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/nz7SB5WS5Csy7uymMIBh600000140_00_00nz7SB5WS5Csy7uymMIBh.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260930/WeHdQCGpAxVMhBizdMLr030086178_00_00WeHdQCGpAxVMhBizdMLr.jpg</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J3" t="n">
-        <v>1611</v>
+        <v>1025</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>뛰어난 가성비와 품질 — 저렴한 가격으로 제약 회사 영양제를 구매할 수 있음</t>
+          <t>상큼하고 맛있는 레몬 맛 — 새콤상큼한 맛으로 호불호 없이 맛있게 먹기 좋음</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>모발 빠짐 개선 느낌 — 지속적으로 먹었을 때 머리카락이 덜 빠지는 듯함</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>알약 크기와 잦은 품절 — 인기 품목이라 품절이 잦으며 알약 크기가 다소 큼</t>
-        </is>
-      </c>
+          <t>분말 형태로 간편한 복용 — 알약을 못 삼키는 사람도 포를 뜯어 가루로 쉽게 섭취 가능함</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>저렴한 가격과 뛰어난 휴대성 — 가격이 저렴하며 주위에 나눠주거나 가지고 다니기 편함</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4609,7 +5123,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>대웅제약 식물성 뉴티지 오메가3 30캡슐 30일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -4619,52 +5133,44 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000203&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20251202/7FdyxsWTlcbRJnDROGoC600000203_00_007FdyxsWTlcbRJnDROGoC.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>1801</v>
+        <v>7100</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>비리지 않은 식물성 원료 — 식물성이라 생선 비린내가 없고 부담 없이 먹을 수 있음</t>
+          <t>소포장의 뛰어난 가성비 — 30일 소포장으로 가격 부담 없이 가성비 좋게 먹기 좋음</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>부드러운 목넘김과 가성비 — 가격이 싸고 캡슐 형태가 부드러워 목넘김이 편리함</t>
+          <t>편안한 숙면 도움 — 매일 챙겨 먹었을 때 잠을 편하게 자는 데 도움을 줌</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>복용 후 묘한 향 올라옴 — 섭취 후 속에서 산초가루 같은 특유의 향이 올라올 수 있음</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>명확하지 않은 체감 효과 — 동물성 대비 뚜렷한 효과를 체감하기 어렵다는 의견이 있음</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4672,12 +5178,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대웅제약 비타민C 30정 30일분</t>
+          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -4687,28 +5193,28 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000127&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953534&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/V0qSVbLLgSaCWbYWEu73600000127_00_00V0qSVbLLgSaCWbYWEu73.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250627/7ii4aNyp1XbM6AH8HjHT994953534_00_007ii4aNyp1XbM6AH8HjHT.jpg</t>
         </is>
       </c>
       <c r="I5" t="n">
         <v>4.8</v>
       </c>
       <c r="J5" t="n">
-        <v>2977</v>
+        <v>1544</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>압도적인 가성비 — 저렴한 가격으로 한 달 분량의 비타민C를 챙길 수 있음</t>
+          <t>이온음료 맛으로 수분 보충 용이 — 맛있는 이온음료 맛이라 맹물보다 수분 섭취량을 늘리기 쉬움</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>구매 및 복용 편의성 — 다이소에서 쉽게 구매하여 매일 꾸준히 섭취하기 좋음</t>
+          <t>짠 음식 섭취 후 밸런스 유지 — 짠 음식을 먹은 뒤 물에 타 마셔서 수분과 전해질을 채우기 좋음</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -4719,7 +5225,7 @@
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4727,7 +5233,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대웅제약 콘드로이친 30정 30일분</t>
+          <t>대웅제약 비타민C 30정 30일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -4742,36 +5248,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000152&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000127&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/b7btdcjQN0UwyzjBmHvY600000152_00_00b7btdcjQN0UwyzjBmHvY.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/V0qSVbLLgSaCWbYWEu73600000127_00_00V0qSVbLLgSaCWbYWEu73.png</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>1313</v>
+        <v>2978</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>저렴한 가격과 빠른 배송 — 가격이 매우 저렴하고 배송이 신속함</t>
+          <t>극강의 가격 대비 성능 — 가격이 매우 저렴하여 부담 없이 구매해 매일 먹기 최적임</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>관절 건강 보조 — 관절에 도움을 줄 것 같아 부담 없이 복용하기 좋음</t>
+          <t>쉬운 구매와 복용 편의 — 필수 영양제를 저렴하고 편리하게 구입해 챙길 수 있음</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>미미한 체감 효과 — 섭취 후 눈에 띄는 효과를 느끼기에는 다소 부족함</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
@@ -4786,7 +5288,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대웅제약 칼슘 120정 30일분</t>
+          <t>대웅제약 비타민B 30정 30일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -4796,48 +5298,44 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000147&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000129&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250409/7vBQfmyyR1zN9NfVg993600000147_00_007vBQfmyyR1zN9NfVg993.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/5QghHD5oyZssCfnGZbzA600000129_00_005QghHD5oyZssCfnGZbzA.png</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>702</v>
+        <v>2413</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>저렴한 뼈 건강 관리 — 다이소에서 합리적인 가격으로 칼슘 영양제를 구입 가능함</t>
+          <t>피로 회복 및 높은 가성비 — 가성비가 뛰어나며 피로 회복용으로 매일 챙겨 먹기 적합함</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>지속 복용 만족감 — 골밀도 감소 및 뼈 건강 걱정 완화에 도움을 줌</t>
+          <t>복용의 용이성 — 부담 없이 매일 꾸준히 복용하기 간편함</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>하루 4정 복용의 부담 — 하루에 4정씩 나눠 먹거나 챙겨 먹어야 해서 다소 부담스러움</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4845,7 +5343,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
+          <t>대웅제약 멀티비타민 미네랄 30정 30일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -4860,43 +5358,39 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000135&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/2ijoJLmHVT94XXIOZnda600000135_00_002ijoJLmHVT94XXIOZnda.png</t>
         </is>
       </c>
       <c r="I8" t="n">
         <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>7578</v>
+        <v>3768</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>혈압 관리와 높은 가성비 — 저렴한 가격에 혈압 관리에 도움을 받을 수 있음</t>
+          <t>하루 한 알 올인원 영양 케어 — 비타민과 미네랄을 한 알로 간편하게 챙길 수 있어 편함</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>하루 1정 간편 복용 — 캡슐 크기가 적당하고 하루 1정만 먹으면 되어 편리함</t>
+          <t>부담 없는 가성비 — 가격이 싸서 지속적으로 재구매하여 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>잦은 일시 품절 — 인기가 많아 재구매 시 일시 품절되는 경우가 많음</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -4904,12 +5398,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>오브맘 기억력 그린라이트 30일분</t>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -4919,43 +5413,39 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=913624077&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250519/l4wgtUT4J6F7QmnnIAOw913624077_00_00l4wgtUT4J6F7QmnnIAOw.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OHEcumxqCcJ047eosRhh600000145_00_00OHEcumxqCcJ047eosRhh.png</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>698</v>
+        <v>6880</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>저렴한 뇌 건강 관리 — 비싼 제품 구매 전 부담 없이 가성비로 챙겨 먹기 좋음</t>
+          <t>높은 가성비와 저렴한 가격 — 가격대가 아주 저렴하여 부담 없이 챙겨 먹는 오메가3임</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>집중력 향상 느낌 — 지속 섭취 시 집중력이 향상되는 듯한 느낌을 줌</t>
+          <t>부담 없는 섭취 제형 — 캡슐을 삼키기 좋고 복용하기 편함</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>효과 불분명함 — 개인에 따라 아무런 체감 효과를 느끼지 못할 수 있음</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4963,12 +5453,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>홀베리 유기농 레몬생강즙 10포</t>
+          <t>대웅제약 식물성 뉴티지 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>홀베리</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -4978,34 +5468,34 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=965923424&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000203&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260904/TyBV46Gp3x0VYWqJvrvs965923424_00_00TyBV46Gp3x0VYWqJvrvs.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20251202/7FdyxsWTlcbRJnDROGoC600000203_00_007FdyxsWTlcbRJnDROGoC.jpg</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>613</v>
+        <v>1801</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>초기 감기 완화 도움 — 감기 기운이 있을 때 따뜻하게 타서 마시기 좋음</t>
+          <t>식물성 원료의 비린내 차단 — 식물성 오메가3라 생선 비린내가 나지 않아 부담이 적음</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>다양한 음료 활용성 — 탄산수나 물에 타서 깔끔하게 마시기 적합함</t>
+          <t>부드러운 목넘김과 개별 편의 — 하루 한 캡슐로 목넘김이 부드럽고 매일 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>알싸하고 매운 생강 맛 — 생강 향이 강하고 매워 개인 취향에 따른 호불호가 있음</t>
+          <t>은은한 속 향기 올라옴 — 섭취 후 속에서 은은한 산초 느낌의 향이 올라올 수 있음</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -5022,12 +5512,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>자연관 이지슬로 엑스트라버진 올리브오일＆레몬 4병</t>
+          <t>닥터블릿 멜라드림 30정 30일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -5037,28 +5527,28 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032627034&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=031930043&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260810/jotmVom4KndGXbIlPcuj032627034_00_01jotmVom4KndGXbIlPcuj.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260106/ifUNcDpBRic8ZZffJeay031930043_00_03ifUNcDpBRic8ZZffJeay.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>1188</v>
+        <v>2065</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>상큼한 레몬 맛과 알뜰함 — 가격이 저렴하고 상큼한 레몬 향으로 맛이 좋음</t>
+          <t>빠른 입면 및 수면 유도 — 복용 후 금방 잠이 올 정도로 숙면에 확실한 도움을 줌</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>아침 공복 섭취 편의 — 개별 병 형태로 아침 공복에 간편하게 마시기 좋음</t>
+          <t>위생적인 포장과 알찬 가성비 — 개별 포장이라 위생적이며 저렴한 가격에 구매 가능함</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -5177,47 +5667,47 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
           <t>루테인/눈건강</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>혈행</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5234,52 +5724,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>락피도</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>홀베리</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>이너뷰 바이 리튠</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>오브맘</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>홀베리</t>
-        </is>
-      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>닥터블릿</t>
         </is>
       </c>
     </row>
@@ -5291,52 +5781,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>락피도 티니핑 쾌변스틱 12포 12일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 맥주효모 비오틴 30정 30일분</t>
+          <t>홀베리 레몬 비타C 500 10개입</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>대웅제약 마그네슘 30정 30일분</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 비타민C 30정 30일분</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 비타민B 30정 30일분</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 멀티비타민 미네랄 30정 30일분</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
           <t>대웅제약 식물성 뉴티지 오메가3 30캡슐 30일분</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 비타민C 30정 30일분</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 콘드로이친 30정 30일분</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 칼슘 120정 30일분</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>오브맘 기억력 그린라이트 30일분</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>홀베리 유기농 레몬생강즙 10포</t>
-        </is>
-      </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>자연관 이지슬로 엑스트라버진 올리브오일＆레몬 4병</t>
+          <t>닥터블릿 멜라드림 30정 30일분</t>
         </is>
       </c>
     </row>
@@ -5350,7 +5840,7 @@
         <v>4.8</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>4.8</v>
@@ -5368,10 +5858,10 @@
         <v>4.8</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>4.8</v>
@@ -5384,37 +5874,37 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>436</v>
+        <v>7586</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1611</v>
+        <v>1025</v>
       </c>
       <c r="E7" s="3" t="n">
+        <v>7100</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>1544</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>2978</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>2413</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>3768</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>6880</v>
+      </c>
+      <c r="K7" s="3" t="n">
         <v>1801</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>2977</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>1313</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>702</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>7578</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>698</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>613</v>
-      </c>
       <c r="L7" s="3" t="n">
-        <v>1188</v>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -5422,107 +5912,83 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>자극 없는 시원한 쾌변 — 배가 아프거나 불편함 없이 자연스러운 쾌변을 도와줌
-맛있는 개별 포장 스틱 — 맛이 좋고 1포씩 개별 포장되어 간편하게 먹을 수 있음</t>
+          <t>부담 없는 뛰어난 가성비 — 가격대가 매우 저렴하여 부담 없이 꾸준히 복용 가능함
+하루 한 알의 간편 복용 — 캡슐 크기가 적당하여 하루 한 알씩 식후 챙겨 먹기 편리함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 가성비와 품질 — 저렴한 가격으로 제약 회사 영양제를 구매할 수 있음
-모발 빠짐 개선 느낌 — 지속적으로 먹었을 때 머리카락이 덜 빠지는 듯함</t>
+          <t>상큼하고 맛있는 레몬 맛 — 새콤상큼한 맛으로 호불호 없이 맛있게 먹기 좋음
+분말 형태로 간편한 복용 — 알약을 못 삼키는 사람도 포를 뜯어 가루로 쉽게 섭취 가능함
+저렴한 가격과 뛰어난 휴대성 — 가격이 저렴하며 주위에 나눠주거나 가지고 다니기 편함</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>비리지 않은 식물성 원료 — 식물성이라 생선 비린내가 없고 부담 없이 먹을 수 있음
-부드러운 목넘김과 가성비 — 가격이 싸고 캡슐 형태가 부드러워 목넘김이 편리함</t>
+          <t>소포장의 뛰어난 가성비 — 30일 소포장으로 가격 부담 없이 가성비 좋게 먹기 좋음
+편안한 숙면 도움 — 매일 챙겨 먹었을 때 잠을 편하게 자는 데 도움을 줌</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>압도적인 가성비 — 저렴한 가격으로 한 달 분량의 비타민C를 챙길 수 있음
-구매 및 복용 편의성 — 다이소에서 쉽게 구매하여 매일 꾸준히 섭취하기 좋음</t>
+          <t>이온음료 맛으로 수분 보충 용이 — 맛있는 이온음료 맛이라 맹물보다 수분 섭취량을 늘리기 쉬움
+짠 음식 섭취 후 밸런스 유지 — 짠 음식을 먹은 뒤 물에 타 마셔서 수분과 전해질을 채우기 좋음</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>저렴한 가격과 빠른 배송 — 가격이 매우 저렴하고 배송이 신속함
-관절 건강 보조 — 관절에 도움을 줄 것 같아 부담 없이 복용하기 좋음</t>
+          <t>극강의 가격 대비 성능 — 가격이 매우 저렴하여 부담 없이 구매해 매일 먹기 최적임
+쉬운 구매와 복용 편의 — 필수 영양제를 저렴하고 편리하게 구입해 챙길 수 있음</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>저렴한 뼈 건강 관리 — 다이소에서 합리적인 가격으로 칼슘 영양제를 구입 가능함
-지속 복용 만족감 — 골밀도 감소 및 뼈 건강 걱정 완화에 도움을 줌</t>
+          <t>피로 회복 및 높은 가성비 — 가성비가 뛰어나며 피로 회복용으로 매일 챙겨 먹기 적합함
+복용의 용이성 — 부담 없이 매일 꾸준히 복용하기 간편함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>혈압 관리와 높은 가성비 — 저렴한 가격에 혈압 관리에 도움을 받을 수 있음
-하루 1정 간편 복용 — 캡슐 크기가 적당하고 하루 1정만 먹으면 되어 편리함</t>
+          <t>하루 한 알 올인원 영양 케어 — 비타민과 미네랄을 한 알로 간편하게 챙길 수 있어 편함
+부담 없는 가성비 — 가격이 싸서 지속적으로 재구매하여 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>저렴한 뇌 건강 관리 — 비싼 제품 구매 전 부담 없이 가성비로 챙겨 먹기 좋음
-집중력 향상 느낌 — 지속 섭취 시 집중력이 향상되는 듯한 느낌을 줌</t>
+          <t>높은 가성비와 저렴한 가격 — 가격대가 아주 저렴하여 부담 없이 챙겨 먹는 오메가3임
+부담 없는 섭취 제형 — 캡슐을 삼키기 좋고 복용하기 편함</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>초기 감기 완화 도움 — 감기 기운이 있을 때 따뜻하게 타서 마시기 좋음
-다양한 음료 활용성 — 탄산수나 물에 타서 깔끔하게 마시기 적합함</t>
+          <t>식물성 원료의 비린내 차단 — 식물성 오메가3라 생선 비린내가 나지 않아 부담이 적음
+부드러운 목넘김과 개별 편의 — 하루 한 캡슐로 목넘김이 부드럽고 매일 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>상큼한 레몬 맛과 알뜰함 — 가격이 저렴하고 상큼한 레몬 향으로 맛이 좋음
-아침 공복 섭취 편의 — 개별 병 형태로 아침 공복에 간편하게 마시기 좋음</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+          <t>빠른 입면 및 수면 유도 — 복용 후 금방 잠이 올 정도로 숙면에 확실한 도움을 줌
+위생적인 포장과 알찬 가성비 — 개별 포장이라 위생적이며 저렴한 가격에 구매 가능함</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>알약 크기와 잦은 품절 — 인기 품목이라 품절이 잦으며 알약 크기가 다소 큼</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>복용 후 묘한 향 올라옴 — 섭취 후 속에서 산초가루 같은 특유의 향이 올라올 수 있음
-명확하지 않은 체감 효과 — 동물성 대비 뚜렷한 효과를 체감하기 어렵다는 의견이 있음</t>
-        </is>
-      </c>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>미미한 체감 효과 — 섭취 후 눈에 띄는 효과를 느끼기에는 다소 부족함</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>하루 4정 복용의 부담 — 하루에 4정씩 나눠 먹거나 챙겨 먹어야 해서 다소 부담스러움</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>잦은 일시 품절 — 인기가 많아 재구매 시 일시 품절되는 경우가 많음</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>효과 불분명함 — 개인에 따라 아무런 체감 효과를 느끼지 못할 수 있음</t>
-        </is>
-      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>알싸하고 매운 생강 맛 — 생강 향이 강하고 매워 개인 취향에 따른 호불호가 있음</t>
+          <t>은은한 속 향기 올라옴 — 섭취 후 속에서 은은한 산초 느낌의 향이 올라올 수 있음</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr"/>
@@ -5540,27 +6006,27 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
+          <t>1,000원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -5668,7 +6134,1055 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:P11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>이미지</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>카테고리</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>순위</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>상품명</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>가격</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>상품URL</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>이미지URL</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>리뷰평점</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>리뷰건수</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>긍정1</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>긍정2</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>긍정3</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>부정1</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>부정2</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>부정3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="38" customHeight="1">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>프로뉴트리션</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>35,800원</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549621ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+    </row>
+    <row r="3" ht="38" customHeight="1">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>생활약속</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>16,200원</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000180121&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018012128ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="38" customHeight="1">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>올더베러 웰니스 구미 30일분 택1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>올더베러</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>10,900원</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245874&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024587422ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+    </row>
+    <row r="5" ht="38" customHeight="1">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>지노마스터</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>27,400원</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492948ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="38" customHeight="1">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>31,400원</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>사은품 굿즈 증정 혜택 — 키링이나 포토카드 등 만족스러운 증정품을 함께 제공함</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2개월분의 넉넉한 기획 구성 — 하루 한 알로 두 달 동안 질유산균을 지속적으로 관리하기 좋음</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+    </row>
+    <row r="7" ht="38" customHeight="1">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>30,400원</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>25774</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+    </row>
+    <row r="8" ht="38" customHeight="1">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>[1+1]알디콤 Plus 숙취해소제 21ml 4포입</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>알디콤</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>17,300원</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000227457&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022745735ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+    </row>
+    <row r="9" ht="38" customHeight="1">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>[추성훈 PICK] 헬스헬퍼 맥스컷 프로 크롬 60캡슐 (10일분)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>헬스헬퍼</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>17,960원</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000237482&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023748215ko.png?l=ko</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+    </row>
+    <row r="10" ht="38" customHeight="1">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>코자아 식물성 멜라토닌 함유 젤리/드링크 (단품/기획)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>코자아</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>32,900원</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000236755&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023675540ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J10" t="n">
+        <v>6071</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>빠르고 깊은 숙면 효과 — 자기 전 복용 시 잠드는 시간이 단축되고 숙면에 효과적임</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>맛있는 포도맛 젤리 제형 — 마이구미 같은 과일 젤리 맛이라 지속적으로 챙겨 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>두통 없는 개운한 아침 — 아침 기상 시 몽롱함이나 두통 없이 컨디션이 개운함</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+    </row>
+    <row r="11" ht="38" customHeight="1">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>푸드올로지</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>18,800원</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000183645&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018364590ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>플랫폼</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>순위</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>1위</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2위</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>3위</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>4위</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>5위</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>6위</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>7위</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>8위</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>9위</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>10위</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="100" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>올리브영</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>썸네일</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>카테고리</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>프로뉴트리션</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>생활약속</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>올더베러</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>지노마스터</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>알디콤</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>헬스헬퍼</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>코자아</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>푸드올로지</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1">
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>상품명</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>올더베러 웰니스 구미 30일분 택1</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>[1+1]알디콤 Plus 숙취해소제 21ml 4포입</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>[추성훈 PICK] 헬스헬퍼 맥스컷 프로 크롬 60캡슐 (10일분)</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>코자아 식물성 멜라토닌 함유 젤리/드링크 (단품/기획)</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>평점</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr"/>
+      <c r="D6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>리뷰수</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="n">
+        <v>25774</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="n">
+        <v>6071</v>
+      </c>
+      <c r="L7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8" ht="90" customHeight="1">
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>긍정리뷰</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>사은품 굿즈 증정 혜택 — 키링이나 포토카드 등 만족스러운 증정품을 함께 제공함
+2개월분의 넉넉한 기획 구성 — 하루 한 알로 두 달 동안 질유산균을 지속적으로 관리하기 좋음</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>빠르고 깊은 숙면 효과 — 자기 전 복용 시 잠드는 시간이 단축되고 숙면에 효과적임
+맛있는 포도맛 젤리 제형 — 마이구미 같은 과일 젤리 맛이라 지속적으로 챙겨 먹기 좋음
+두통 없는 개운한 아침 — 아침 기상 시 몽롱함이나 두통 없이 컨디션이 개운함</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>부정리뷰</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>판매가</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>35,800원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>16,200원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>10,900원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>27,400원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>31,400원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>30,400원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>17,300원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>17,960원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>32,900원</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>18,800원</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>링크</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:A11"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5697,6 +7211,11 @@
           <t>다이소몰</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>올리브영</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5705,15 +7224,18 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>36.7</v>
+        <v>37.5</v>
       </c>
       <c r="D2" t="n">
         <v>6</v>
       </c>
       <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5724,15 +7246,18 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>23.3</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
         <v>7</v>
       </c>
       <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5743,111 +7268,173 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>16.7</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>6.7</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
         <v>0</v>
       </c>
-      <c r="E8" t="n">
-        <v>1</v>
+      <c r="F8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>피부/미용</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
